--- a/Templates/water-quality-analysis/example-template-gb.xlsx
+++ b/Templates/water-quality-analysis/example-template-gb.xlsx
@@ -1,46 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wampleka\Documents\Projects\WWS-standard-methods\Templates\water-quality-analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nussdore\Documents\GitHub\WWS-standard-methods\Templates\water-quality-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26D0C14-D382-400C-9A13-A7ADEFF59F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2C2916-89E3-4E0F-8B23-F9E65578DCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sample-DateTime" sheetId="21" state="visible" r:id="rId1"/>
-    <sheet name="Labels-Field" sheetId="11" state="visible" r:id="rId2"/>
-    <sheet name="Labels-Lab" sheetId="7" state="visible" r:id="rId3"/>
-    <sheet name="DS-Filter Weight" sheetId="18" state="visible" r:id="rId4"/>
-    <sheet name="DS-Bottle Numbers" sheetId="16" state="visible" r:id="rId5"/>
-    <sheet name="DS-ISCO Bottle Weight" sheetId="17" state="visible" r:id="rId6"/>
+    <sheet name="Sample-DateTime" sheetId="21" r:id="rId1"/>
+    <sheet name="Labels-Field" sheetId="11" r:id="rId2"/>
+    <sheet name="Labels-Lab" sheetId="7" r:id="rId3"/>
+    <sheet name="DS-Filter Weight" sheetId="18" r:id="rId4"/>
+    <sheet name="DS-Bottle Numbers" sheetId="16" r:id="rId5"/>
+    <sheet name="DS-ISCO Bottle Weight" sheetId="17" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="150">
   <si>
     <t>Site</t>
   </si>
@@ -118,13 +108,385 @@
   </si>
   <si>
     <t>Random Number</t>
+  </si>
+  <si>
+    <t>BDRK_R0016</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_____________</t>
+  </si>
+  <si>
+    <t>B01M</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>BDRK_R0005</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_____________</t>
+  </si>
+  <si>
+    <t>B02H</t>
+  </si>
+  <si>
+    <t>BDRK_R0007</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_____________</t>
+  </si>
+  <si>
+    <t>B03H</t>
+  </si>
+  <si>
+    <t>BDRK_R0017</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_____________</t>
+  </si>
+  <si>
+    <t>B04M</t>
+  </si>
+  <si>
+    <t>BDRK_R0020</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_____________</t>
+  </si>
+  <si>
+    <t>B05H</t>
+  </si>
+  <si>
+    <t>BDRK_R0015</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_____________</t>
+  </si>
+  <si>
+    <t>B06H</t>
+  </si>
+  <si>
+    <t>BDRK_R0002</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_____________</t>
+  </si>
+  <si>
+    <t>B07H</t>
+  </si>
+  <si>
+    <t>BDRK_R0011</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_____________</t>
+  </si>
+  <si>
+    <t>B08M</t>
+  </si>
+  <si>
+    <t>BDRK_R0004</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_____________</t>
+  </si>
+  <si>
+    <t>B09H</t>
+  </si>
+  <si>
+    <t>BDRK_R0014</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_____________</t>
+  </si>
+  <si>
+    <t>B10M</t>
+  </si>
+  <si>
+    <t>BDRK_R0019</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_____________</t>
+  </si>
+  <si>
+    <t>U11H</t>
+  </si>
+  <si>
+    <t>BDRK_R0009</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_____________</t>
+  </si>
+  <si>
+    <t>U12M</t>
+  </si>
+  <si>
+    <t>BDRK_R0006</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_____________</t>
+  </si>
+  <si>
+    <t>U13H</t>
+  </si>
+  <si>
+    <t>BDRK_R0001</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_____________</t>
+  </si>
+  <si>
+    <t>U14H</t>
+  </si>
+  <si>
+    <t>BDRK_R0008</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_____________</t>
+  </si>
+  <si>
+    <t>U15H</t>
+  </si>
+  <si>
+    <t>BDRK_R0012</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_____________</t>
+  </si>
+  <si>
+    <t>U16M</t>
+  </si>
+  <si>
+    <t>BDRK_R0018</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_____________</t>
+  </si>
+  <si>
+    <t>U17H</t>
+  </si>
+  <si>
+    <t>BDRK_R0010</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_____________</t>
+  </si>
+  <si>
+    <t>U18H</t>
+  </si>
+  <si>
+    <t>BDRK_R0003</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_____________</t>
+  </si>
+  <si>
+    <t>U19M</t>
+  </si>
+  <si>
+    <t>BDRK_R0013</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_____________</t>
+  </si>
+  <si>
+    <t>C20M</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260823_1200_CN</t>
+  </si>
+  <si>
+    <t>Shimadzu</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260823_1200_AQ</t>
+  </si>
+  <si>
+    <t>Aqualog</t>
+  </si>
+  <si>
+    <t>BDRK_U14H_GB_20260823_1200_LV</t>
+  </si>
+  <si>
+    <t>Levoglucosan</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260823_1700_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260823_1700_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B07H_GB_20260823_1700_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260823_2000_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260823_2000_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U19M_GB_20260823_2000_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260823_1900_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260823_1900_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B09H_GB_20260823_1900_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260823_0830_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260823_0830_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B02H_GB_20260823_0830_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260823_1000_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260823_1000_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U13H_GB_20260823_1000_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260823_0900_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260823_0900_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B03H_GB_20260823_0900_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260823_1500_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260823_1500_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U15H_GB_20260823_1500_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260823_0900_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260823_0900_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U12M_GB_20260823_0900_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260823_1900_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260823_1900_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U18H_GB_20260823_1900_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260823_1800_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260823_1800_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B08M_GB_20260823_1800_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260823_1700_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260823_1700_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U16M_GB_20260823_1700_LV</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260823_2100_CN</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260823_2100_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_C20M_GB_20260823_2100_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260823_0800_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260823_0800_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B10M_GB_20260823_0800_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260823_1500_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260823_1500_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B06H_GB_20260823_1500_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260823_0800_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260823_0800_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B01M_GB_20260823_0800_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260823_1000_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260823_1000_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B04M_GB_20260823_1000_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260823_1800_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260823_1800_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U17H_GB_20260823_1800_LV</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260823_0830_CN</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260823_0830_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_U11H_GB_20260823_0830_LV</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260823_1200_CN</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260823_1200_AQ</t>
+  </si>
+  <si>
+    <t>BDRK_B05H_GB_20260823_1200_LV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,20 +1346,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1020,26 +1382,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>B01M</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
       </c>
       <c r="E2">
         <v>16</v>
@@ -1051,26 +1405,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B02H</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -1082,26 +1428,18 @@
         <v>830</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>B03H</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1113,26 +1451,18 @@
         <v>900</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>B04M</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
       </c>
       <c r="E5">
         <v>17</v>
@@ -1144,26 +1474,18 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>B05H</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -1175,26 +1497,18 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>B06H</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1206,26 +1520,18 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B07H</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1237,26 +1543,18 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B08M</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
       </c>
       <c r="E9">
         <v>11</v>
@@ -1268,26 +1566,18 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>B09H</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -1299,26 +1589,18 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B10M</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -1330,26 +1612,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>U11H</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
       </c>
       <c r="E12">
         <v>19</v>
@@ -1361,26 +1635,18 @@
         <v>830</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>U12M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -1392,26 +1658,18 @@
         <v>900</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>U13H</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1423,26 +1681,18 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>U14H</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1454,26 +1704,18 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>U15H</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -1485,26 +1727,18 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>U16M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
       </c>
       <c r="E17">
         <v>12</v>
@@ -1516,26 +1750,18 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>U17H</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
       </c>
       <c r="E18">
         <v>18</v>
@@ -1547,26 +1773,18 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_____________</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>U18H</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -1578,26 +1796,18 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>U19M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1609,26 +1819,18 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_____________</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>C20M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
       </c>
       <c r="E21">
         <v>13</v>
@@ -1645,38 +1847,24 @@
     <cfRule type="cellIs" dxfId="37" priority="9" operator="equal">
       <formula>"BPCA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="36" priority="10" operator="equal">
       <formula>"Grab"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="35" priority="11" operator="equal">
       <formula>"ISCO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="34" priority="12" operator="equal">
       <formula>"Excess"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="33" priority="13" operator="equal">
       <formula>"CCAL"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="32" priority="14" operator="equal">
       <formula>"Levoglucosan"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="31" priority="15" operator="equal">
       <formula>"Aqualog"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="30" priority="16" operator="equal">
       <formula>"Shimadzu"</formula>
     </cfRule>
@@ -1685,38 +1873,24 @@
     <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"BPCA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Grab"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"ISCO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
       <formula>"Excess"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
       <formula>"CCAL"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"Levoglucosan"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"Aqualog"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
       <formula>"Shimadzu"</formula>
     </cfRule>
@@ -1726,16 +1900,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1751,38 +1925,24 @@
     <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"BPCA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"Grab"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"ISCO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
       <formula>"Excess"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"CCAL"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"Levoglucosan"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"Aqualog"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A283">
     <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"Shimadzu"</formula>
     </cfRule>
@@ -1792,19 +1952,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.453125" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -1815,1024 +1975,664 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_20260823_1200_CN</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_20260823_1200_AQ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_20260823_1200_LV</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_20260823_1700_CN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_20260823_1700_AQ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_20260823_1700_LV</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_20260823_2000_CN</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_20260823_2000_AQ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_20260823_2000_LV</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_20260823_1900_CN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_20260823_1900_AQ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_20260823_1900_LV</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_20260823_0830_CN</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_20260823_0830_AQ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_20260823_0830_LV</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_20260823_1000_CN</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_20260823_1000_AQ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_20260823_1000_LV</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_20260823_0900_CN</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_20260823_0900_AQ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_20260823_0900_LV</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_20260823_1500_CN</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_20260823_1500_AQ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_20260823_1500_LV</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_20260823_0900_CN</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_20260823_0900_AQ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_20260823_0900_LV</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_20260823_1900_CN</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_20260823_1900_AQ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_20260823_1900_LV</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_20260823_1800_CN</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_20260823_1800_AQ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_20260823_1800_LV</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_20260823_1700_CN</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_20260823_1700_AQ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_20260823_1700_LV</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_20260823_2100_CN</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_20260823_2100_AQ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_20260823_2100_LV</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_20260823_0800_CN</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_20260823_0800_AQ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_20260823_0800_LV</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_20260823_1500_CN</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_20260823_1500_AQ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_20260823_1500_LV</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_20260823_0800_CN</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_20260823_0800_AQ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_20260823_0800_LV</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_20260823_1000_CN</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_20260823_1000_AQ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_20260823_1000_LV</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_20260823_1800_CN</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_20260823_1800_AQ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_20260823_1800_LV</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_20260823_0830_CN</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_20260823_0830_AQ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_20260823_0830_LV</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_20260823_1200_CN</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_20260823_1200_AQ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Aqualog</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_20260823_1200_LV</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Levoglucosan</t>
-        </is>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>145</v>
+      </c>
+      <c r="C57" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2841,33 +2641,21 @@
     <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
       <formula>"Grab"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
       <formula>"ISCO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"Excess"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"CCAL"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"Levoglucosan"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
       <formula>"Aqualog"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"Shimadzu"</formula>
     </cfRule>
@@ -2876,40 +2664,28 @@
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"Grab"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"ISCO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"Excess"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"CCAL"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"Levoglucosan"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"Aqualog"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
     <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"Shimadzu"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="86" fitToHeight="0" orientation="landscape"/>
-  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;13Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Regular"&amp;14&amp;P of &amp;N</oddFooter>
@@ -2918,21 +2694,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" style="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="36.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="36.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>14</v>
       </c>
@@ -2945,7 +2721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>19</v>
       </c>
@@ -2962,839 +2738,759 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_____________</t>
-        </is>
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_____________</t>
-        </is>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_____________</t>
-        </is>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_____________</t>
-        </is>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_____________</t>
-        </is>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_____________</t>
-        </is>
+    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_____________</t>
-        </is>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_____________</t>
-        </is>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_____________</t>
-        </is>
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_____________</t>
-        </is>
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_____________</t>
-        </is>
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_____________</t>
-        </is>
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_____________</t>
-        </is>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_____________</t>
-        </is>
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_____________</t>
-        </is>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_____________</t>
-        </is>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_____________</t>
-        </is>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_____________</t>
-        </is>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_____________</t>
-        </is>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_____________</t>
-        </is>
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="11"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="12"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="11"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="12"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="11"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="12"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="11"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="12"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="11"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="12"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="11"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="12"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="11"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="12"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="11"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="12"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="11"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="12"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="11"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="12"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="11"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="12"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="11"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="12"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="11"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="12"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="11"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="12"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="11"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="12"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="11"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="12"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="11"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="12"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
     </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="11"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="12"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="11"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="12"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="11"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="12"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="11"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="12"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="11"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="12"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="11"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="12"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="11"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="12"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="11"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="12"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="11"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="12"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="11"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="12"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
     </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="11"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="12"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
     </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="11"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="12"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
     </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="11"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="12"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
     </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="11"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="12"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
     </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="11"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="12"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
     </row>
-    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="11"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="12"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
     </row>
-    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="11"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="12"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
     </row>
-    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="11"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="12"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
     </row>
-    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="11"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="12"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
     </row>
-    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="11"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="12"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
     </row>
-    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="11"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="12"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
     </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="11"/>
       <c r="C99" s="3"/>
@@ -3808,7 +3504,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" fitToHeight="0" orientation="portrait"/>
-  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Bold"&amp;14&amp;P of &amp;N</oddFooter>
@@ -3817,23 +3513,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="7" max="7" width="33.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>2</v>
       </c>
@@ -3854,7 +3550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>19</v>
       </c>
@@ -3877,16 +3573,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_____________</t>
-        </is>
+    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -3894,16 +3586,12 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_____________</t>
-        </is>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -3911,16 +3599,12 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_____________</t>
-        </is>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3928,16 +3612,12 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_____________</t>
-        </is>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3945,16 +3625,12 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_____________</t>
-        </is>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -3962,16 +3638,12 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_____________</t>
-        </is>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -3979,16 +3651,12 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_____________</t>
-        </is>
+    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -3996,16 +3664,12 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_____________</t>
-        </is>
+    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4013,16 +3677,12 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_____________</t>
-        </is>
+    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -4030,16 +3690,12 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_____________</t>
-        </is>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -4047,16 +3703,12 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_____________</t>
-        </is>
+    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -4064,16 +3716,12 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_____________</t>
-        </is>
+    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -4081,16 +3729,12 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_____________</t>
-        </is>
+    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -4098,16 +3742,12 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_____________</t>
-        </is>
+    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -4115,16 +3755,12 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_____________</t>
-        </is>
+    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -4132,16 +3768,12 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_____________</t>
-        </is>
+    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -4149,16 +3781,12 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_____________</t>
-        </is>
+    <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -4166,16 +3794,12 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_____________</t>
-        </is>
+    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -4183,16 +3807,12 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_____________</t>
-        </is>
+    <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -4200,16 +3820,12 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_____________</t>
-        </is>
+    <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -4217,7 +3833,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="C23" s="5"/>
@@ -4226,7 +3842,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="12"/>
       <c r="C24" s="4"/>
@@ -4235,7 +3851,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="13"/>
       <c r="C25" s="5"/>
@@ -4244,7 +3860,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="12"/>
       <c r="C26" s="4"/>
@@ -4253,7 +3869,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="13"/>
       <c r="C27" s="5"/>
@@ -4262,7 +3878,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="12"/>
       <c r="C28" s="4"/>
@@ -4271,7 +3887,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="13"/>
       <c r="C29" s="5"/>
@@ -4280,7 +3896,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="12"/>
       <c r="C30" s="4"/>
@@ -4289,7 +3905,7 @@
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="13"/>
       <c r="C31" s="5"/>
@@ -4298,7 +3914,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="12"/>
       <c r="C32" s="4"/>
@@ -4307,7 +3923,7 @@
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="13"/>
       <c r="C33" s="5"/>
@@ -4316,7 +3932,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="12"/>
       <c r="C34" s="4"/>
@@ -4325,7 +3941,7 @@
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="13"/>
       <c r="C35" s="5"/>
@@ -4334,7 +3950,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="12"/>
       <c r="C36" s="4"/>
@@ -4343,7 +3959,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="13"/>
       <c r="C37" s="5"/>
@@ -4352,7 +3968,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
-    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="12"/>
       <c r="C38" s="4"/>
@@ -4361,7 +3977,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="13"/>
       <c r="C39" s="5"/>
@@ -4370,7 +3986,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="12"/>
       <c r="C40" s="4"/>
@@ -4379,7 +3995,7 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="13"/>
       <c r="C41" s="5"/>
@@ -4388,7 +4004,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="12"/>
       <c r="C42" s="4"/>
@@ -4397,7 +4013,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
     </row>
-    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="13"/>
       <c r="C43" s="5"/>
@@ -4406,7 +4022,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
     </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="12"/>
       <c r="C44" s="4"/>
@@ -4415,7 +4031,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
     </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="13"/>
       <c r="C45" s="5"/>
@@ -4424,7 +4040,7 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="12"/>
       <c r="C46" s="4"/>
@@ -4433,7 +4049,7 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="13"/>
       <c r="C47" s="5"/>
@@ -4442,7 +4058,7 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="12"/>
       <c r="C48" s="4"/>
@@ -4451,7 +4067,7 @@
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="13"/>
       <c r="C49" s="5"/>
@@ -4460,7 +4076,7 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
     </row>
-    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="12"/>
       <c r="C50" s="4"/>
@@ -4469,7 +4085,7 @@
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="13"/>
       <c r="C51" s="5"/>
@@ -4478,7 +4094,7 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
     </row>
-    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="12"/>
       <c r="C52" s="4"/>
@@ -4487,7 +4103,7 @@
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
     </row>
-    <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="13"/>
       <c r="C53" s="5"/>
@@ -4496,7 +4112,7 @@
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
     </row>
-    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="12"/>
       <c r="C54" s="4"/>
@@ -4505,7 +4121,7 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="13"/>
       <c r="C55" s="5"/>
@@ -4514,7 +4130,7 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
     </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="12"/>
       <c r="C56" s="4"/>
@@ -4523,7 +4139,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
     </row>
-    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="13"/>
       <c r="C57" s="5"/>
@@ -4532,7 +4148,7 @@
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
     </row>
-    <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="12"/>
       <c r="C58" s="4"/>
@@ -4541,7 +4157,7 @@
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
     </row>
-    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="13"/>
       <c r="C59" s="5"/>
@@ -4550,7 +4166,7 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
     </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="12"/>
       <c r="C60" s="4"/>
@@ -4559,7 +4175,7 @@
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
     </row>
-    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="13"/>
       <c r="C61" s="5"/>
@@ -4568,7 +4184,7 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
     </row>
-    <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="12"/>
       <c r="C62" s="4"/>
@@ -4577,7 +4193,7 @@
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="13"/>
       <c r="C63" s="5"/>
@@ -4586,7 +4202,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
     </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="12"/>
       <c r="C64" s="4"/>
@@ -4595,7 +4211,7 @@
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="13"/>
       <c r="C65" s="5"/>
@@ -4604,7 +4220,7 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="12"/>
       <c r="C66" s="4"/>
@@ -4613,7 +4229,7 @@
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="13"/>
       <c r="C67" s="5"/>
@@ -4622,7 +4238,7 @@
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
     </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="12"/>
       <c r="C68" s="4"/>
@@ -4631,7 +4247,7 @@
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
     </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="13"/>
       <c r="C69" s="5"/>
@@ -4640,7 +4256,7 @@
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
     </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="12"/>
       <c r="C70" s="4"/>
@@ -4649,7 +4265,7 @@
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="13"/>
       <c r="C71" s="5"/>
@@ -4658,7 +4274,7 @@
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="12"/>
       <c r="C72" s="4"/>
@@ -4667,7 +4283,7 @@
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="13"/>
       <c r="C73" s="5"/>
@@ -4676,7 +4292,7 @@
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="12"/>
       <c r="C74" s="4"/>
@@ -4685,7 +4301,7 @@
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
     </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="13"/>
       <c r="C75" s="5"/>
@@ -4694,7 +4310,7 @@
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="12"/>
       <c r="C76" s="4"/>
@@ -4703,7 +4319,7 @@
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="13"/>
       <c r="C77" s="5"/>
@@ -4712,7 +4328,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="12"/>
       <c r="C78" s="4"/>
@@ -4721,7 +4337,7 @@
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
     </row>
-    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="13"/>
       <c r="C79" s="5"/>
@@ -4730,7 +4346,7 @@
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="12"/>
       <c r="C80" s="4"/>
@@ -4739,7 +4355,7 @@
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
     </row>
-    <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
       <c r="B81" s="13"/>
       <c r="C81" s="5"/>
@@ -4748,7 +4364,7 @@
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
     </row>
-    <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="12"/>
       <c r="C82" s="4"/>
@@ -4757,7 +4373,7 @@
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
     </row>
-    <row r="83" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="5"/>
       <c r="B83" s="13"/>
       <c r="C83" s="5"/>
@@ -4766,7 +4382,7 @@
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
     </row>
-    <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="12"/>
       <c r="C84" s="4"/>
@@ -4775,7 +4391,7 @@
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
     </row>
-    <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="5"/>
       <c r="B85" s="13"/>
       <c r="C85" s="5"/>
@@ -4784,7 +4400,7 @@
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
-    <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="12"/>
       <c r="C86" s="4"/>
@@ -4793,7 +4409,7 @@
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
     </row>
-    <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="5"/>
       <c r="B87" s="13"/>
       <c r="C87" s="5"/>
@@ -4802,7 +4418,7 @@
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
-    <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="12"/>
       <c r="C88" s="4"/>
@@ -4811,7 +4427,7 @@
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
     </row>
-    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="5"/>
       <c r="B89" s="13"/>
       <c r="C89" s="5"/>
@@ -4820,7 +4436,7 @@
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
-    <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="12"/>
       <c r="C90" s="4"/>
@@ -4829,7 +4445,7 @@
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
     </row>
-    <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="5"/>
       <c r="B91" s="13"/>
       <c r="C91" s="5"/>
@@ -4838,7 +4454,7 @@
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
-    <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="12"/>
       <c r="C92" s="4"/>
@@ -4847,7 +4463,7 @@
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
     </row>
-    <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="5"/>
       <c r="B93" s="13"/>
       <c r="C93" s="5"/>
@@ -4856,7 +4472,7 @@
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
-    <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="12"/>
       <c r="C94" s="4"/>
@@ -4871,7 +4487,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="95" fitToHeight="0" orientation="landscape"/>
-  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Bold"&amp;14&amp;P of &amp;N</oddFooter>
@@ -4880,21 +4496,21 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" style="14" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
@@ -4907,7 +4523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>19</v>
       </c>
@@ -4924,839 +4540,759 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0001</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U14H_GB_____________</t>
-        </is>
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0002</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B07H_GB_____________</t>
-        </is>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0003</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U19M_GB_____________</t>
-        </is>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0004</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B09H_GB_____________</t>
-        </is>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0005</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B02H_GB_____________</t>
-        </is>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0006</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U13H_GB_____________</t>
-        </is>
+    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0007</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B03H_GB_____________</t>
-        </is>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0008</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U15H_GB_____________</t>
-        </is>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0009</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U12M_GB_____________</t>
-        </is>
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0010</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U18H_GB_____________</t>
-        </is>
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0011</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B08M_GB_____________</t>
-        </is>
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0012</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U16M_GB_____________</t>
-        </is>
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0013</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_C20M_GB_____________</t>
-        </is>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0014</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B10M_GB_____________</t>
-        </is>
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0015</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B06H_GB_____________</t>
-        </is>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0016</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B01M_GB_____________</t>
-        </is>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0017</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_B04M_GB_____________</t>
-        </is>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0018</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_U17H_GB_____________</t>
-        </is>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>BDRK_R0019</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>BDRK_U11H_GB_____________</t>
-        </is>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>BDRK_R0020</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>BDRK_B05H_GB_____________</t>
-        </is>
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="11"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="12"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="11"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="12"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="11"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="12"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="11"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="12"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="11"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="12"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="11"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="12"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="11"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="12"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="11"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="12"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="11"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="12"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="11"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="12"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="11"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="12"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
     </row>
-    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="11"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="12"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="11"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="12"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="11"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="12"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="11"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="12"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="11"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="12"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="11"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="12"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
     </row>
-    <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="11"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="12"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="11"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="12"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="11"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="12"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="11"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="12"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="11"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="12"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
-    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="11"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="12"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="11"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="12"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
     </row>
-    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="11"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="12"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="11"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="12"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="11"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="12"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
     </row>
-    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="11"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="12"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
     </row>
-    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="11"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="12"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
     </row>
-    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="11"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="12"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
     </row>
-    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="11"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
     </row>
-    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="12"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
     </row>
-    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="11"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
     </row>
-    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="12"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
     </row>
-    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="11"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="12"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
     </row>
-    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="11"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="12"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
     </row>
-    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="11"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="12"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
     </row>
-    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="11"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
     </row>
-    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="12"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
     </row>
-    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="11"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="12"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
     </row>
-    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="11"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="12"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
     </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="11"/>
       <c r="C99" s="3"/>
@@ -5769,8 +5305,8 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="98" fitToHeight="0" orientation="portrait"/>
-  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+  <pageSetup scale="84" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;"Consolas,Bold"&amp;12Date:____________________ Technican:___________________ 
 Project Code:___________  Study Code:_____________</oddHeader>
     <oddFooter>&amp;C&amp;"Consolas,Bold"&amp;14&amp;P of &amp;N</oddFooter>
